--- a/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260609.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260609.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D74"/>
+  <dimension ref="A1:D73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -623,17 +623,17 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>68,000,000</t>
+          <t>8,960,000</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -645,17 +645,17 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>8,960,000</t>
+          <t>68,000,000</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>1,080,000</t>
+          <t>1,380,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>1,380,000</t>
+          <t>1,080,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1761,28 +1761,6 @@
       <c r="D73" s="4" t="inlineStr">
         <is>
           <t>-0.49%</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="3" t="inlineStr">
-        <is>
-          <t>PFUR_NTD</t>
-        </is>
-      </c>
-      <c r="B74" s="3" t="inlineStr">
-        <is>
-          <t>PAYABLES FOR UNITS REDEEMED</t>
-        </is>
-      </c>
-      <c r="C74" s="4" t="inlineStr">
-        <is>
-          <t>-1,983,688,440</t>
-        </is>
-      </c>
-      <c r="D74" s="4" t="inlineStr">
-        <is>
-          <t>-1.09%</t>
         </is>
       </c>
     </row>
